--- a/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>GATO</t>
   </si>
@@ -656,109 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>40633</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -825,8 +828,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -887,14 +893,17 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3">
         <v>1200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -955,14 +964,17 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3">
         <v>-1200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,8 +999,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -998,11 +1011,11 @@
       <c r="E12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>4</v>
@@ -1010,53 +1023,56 @@
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,13 +1139,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>1500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1137,32 +1156,32 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>80300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1191,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1229,38 +1251,41 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>1200</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1700</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,76 +1307,80 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>84300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-4200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,67 +1388,70 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-84300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18500</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1476,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1453,67 +1486,70 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>19900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-23800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-15000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-14800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,84 +1557,87 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-62500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1600</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-16000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-17700</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1607,28 +1646,28 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
         <v>3900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
@@ -1642,108 +1681,114 @@
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>12400</v>
       </c>
       <c r="E23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-62700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-22900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1757,8 +1802,8 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>4</v>
@@ -1766,8 +1811,8 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1784,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>12300</v>
       </c>
       <c r="E26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-62700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-22900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>12300</v>
       </c>
       <c r="E27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-62700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-22900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2082,8 +2142,8 @@
       <c r="J29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2095,25 +2155,25 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-5400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3">
         <v>-1800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-6900</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2326,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2269,135 +2338,141 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-19900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>23800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>14800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>12300</v>
       </c>
       <c r="E33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-62700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-22900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>12300</v>
       </c>
       <c r="E35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-62700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-22900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>40633</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,52 +2742,53 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E41" s="3">
         <v>33500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>2000</v>
       </c>
       <c r="P41" s="3">
         <v>2000</v>
       </c>
       <c r="Q41" s="3">
-        <v>9100</v>
+        <v>2000</v>
       </c>
       <c r="R41" s="3">
         <v>9100</v>
@@ -2711,11 +2797,11 @@
         <v>9100</v>
       </c>
       <c r="T41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="U41" s="3">
         <v>15600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2725,8 +2811,11 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,52 +2882,55 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16100</v>
+        <v>21300</v>
       </c>
       <c r="E43" s="3">
         <v>16100</v>
       </c>
       <c r="F43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5200</v>
-      </c>
-      <c r="O43" s="3">
-        <v>10000</v>
       </c>
       <c r="P43" s="3">
         <v>10000</v>
       </c>
       <c r="Q43" s="3">
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="R43" s="3">
         <v>6600</v>
@@ -2847,11 +2939,11 @@
         <v>6600</v>
       </c>
       <c r="T43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2861,8 +2953,11 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2900,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -2917,8 +3012,8 @@
       <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
+      <c r="U44" s="3">
+        <v>100</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>4</v>
@@ -2929,52 +3024,55 @@
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3400</v>
       </c>
       <c r="P45" s="3">
         <v>3400</v>
       </c>
       <c r="Q45" s="3">
-        <v>2600</v>
+        <v>3400</v>
       </c>
       <c r="R45" s="3">
         <v>2600</v>
@@ -2983,11 +3081,11 @@
         <v>2600</v>
       </c>
       <c r="T45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U45" s="3">
         <v>5900</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2997,52 +3095,55 @@
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E46" s="3">
         <v>50500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39600</v>
-      </c>
-      <c r="O46" s="3">
-        <v>15500</v>
       </c>
       <c r="P46" s="3">
         <v>15500</v>
       </c>
       <c r="Q46" s="3">
-        <v>18500</v>
+        <v>15500</v>
       </c>
       <c r="R46" s="3">
         <v>18500</v>
@@ -3051,11 +3152,11 @@
         <v>18500</v>
       </c>
       <c r="T46" s="3">
+        <v>18500</v>
+      </c>
+      <c r="U46" s="3">
         <v>21800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3065,52 +3166,55 @@
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>321900</v>
+      </c>
+      <c r="E47" s="3">
         <v>328700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>354300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>352800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>347800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>341100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>342600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>379800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>333400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>393600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>247300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>226100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>91500</v>
       </c>
       <c r="P47" s="3">
         <v>91500</v>
       </c>
       <c r="Q47" s="3">
-        <v>105400</v>
+        <v>91500</v>
       </c>
       <c r="R47" s="3">
         <v>105400</v>
@@ -3119,11 +3223,11 @@
         <v>105400</v>
       </c>
       <c r="T47" s="3">
+        <v>105400</v>
+      </c>
+      <c r="U47" s="3">
         <v>114400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3133,8 +3237,11 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3162,8 +3269,8 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
+      <c r="L48" s="3">
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
@@ -3171,14 +3278,14 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>29000</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>29000</v>
       </c>
       <c r="Q48" s="3">
-        <v>30200</v>
+        <v>29000</v>
       </c>
       <c r="R48" s="3">
         <v>30200</v>
@@ -3187,11 +3294,11 @@
         <v>30200</v>
       </c>
       <c r="T48" s="3">
+        <v>30200</v>
+      </c>
+      <c r="U48" s="3">
         <v>30800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3201,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,25 +3521,28 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -3441,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>300</v>
@@ -3461,8 +3580,8 @@
       <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
+      <c r="U52" s="3">
+        <v>300</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,52 +3663,55 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E54" s="3">
         <v>379300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>381300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>382800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>383500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>358000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>352800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>388600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>345200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>408400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>284600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>265700</v>
-      </c>
-      <c r="O54" s="3">
-        <v>136100</v>
       </c>
       <c r="P54" s="3">
         <v>136100</v>
       </c>
       <c r="Q54" s="3">
-        <v>154300</v>
+        <v>136100</v>
       </c>
       <c r="R54" s="3">
         <v>154300</v>
@@ -3595,11 +3720,11 @@
         <v>154300</v>
       </c>
       <c r="T54" s="3">
+        <v>154300</v>
+      </c>
+      <c r="U54" s="3">
         <v>167200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3609,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,52 +3790,53 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>500</v>
       </c>
       <c r="G57" s="3">
+        <v>500</v>
+      </c>
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>600</v>
       </c>
       <c r="O57" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>700</v>
       </c>
       <c r="Q57" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="R57" s="3">
         <v>300</v>
@@ -3717,8 +3847,8 @@
       <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
+      <c r="U57" s="3">
+        <v>300</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
@@ -3729,8 +3859,11 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3768,13 +3901,13 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>10000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3">
+        <v>10000</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
@@ -3797,52 +3930,55 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E59" s="3">
         <v>25300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>2400</v>
       </c>
       <c r="P59" s="3">
         <v>2400</v>
       </c>
       <c r="Q59" s="3">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="R59" s="3">
         <v>3200</v>
@@ -3851,11 +3987,11 @@
         <v>3200</v>
       </c>
       <c r="T59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3865,52 +4001,55 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>33400</v>
       </c>
       <c r="E60" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F60" s="3">
         <v>25700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>13000</v>
       </c>
       <c r="P60" s="3">
         <v>13000</v>
       </c>
       <c r="Q60" s="3">
-        <v>3500</v>
+        <v>13000</v>
       </c>
       <c r="R60" s="3">
         <v>3500</v>
@@ -3919,11 +4058,11 @@
         <v>3500</v>
       </c>
       <c r="T60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3933,8 +4072,11 @@
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3942,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>8700</v>
@@ -3951,7 +4093,7 @@
         <v>8700</v>
       </c>
       <c r="H61" s="3">
-        <v>12700</v>
+        <v>8700</v>
       </c>
       <c r="I61" s="3">
         <v>12700</v>
@@ -3960,13 +4102,13 @@
         <v>12700</v>
       </c>
       <c r="K61" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="L61" s="3">
         <v>12600</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -4001,8 +4143,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4040,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>1500</v>
       </c>
       <c r="Q62" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="R62" s="3">
         <v>1400</v>
@@ -4057,8 +4202,8 @@
       <c r="T62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="U62" s="3">
+        <v>1400</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,52 +4427,55 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>33400</v>
       </c>
       <c r="E66" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F66" s="3">
         <v>34400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>14500</v>
       </c>
       <c r="P66" s="3">
         <v>14500</v>
       </c>
       <c r="Q66" s="3">
-        <v>4900</v>
+        <v>14500</v>
       </c>
       <c r="R66" s="3">
         <v>4900</v>
@@ -4327,11 +4484,11 @@
         <v>4900</v>
       </c>
       <c r="T66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U66" s="3">
         <v>3600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4341,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,52 +4809,55 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-185900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-198200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-201500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-197900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-198700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-203500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-207000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-172000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-213300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-150600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-135600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-149000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-255500</v>
       </c>
       <c r="P72" s="3">
         <v>-255500</v>
       </c>
       <c r="Q72" s="3">
-        <v>-225600</v>
+        <v>-255500</v>
       </c>
       <c r="R72" s="3">
         <v>-225600</v>
@@ -4693,11 +4866,11 @@
         <v>-225600</v>
       </c>
       <c r="T72" s="3">
+        <v>-225600</v>
+      </c>
+      <c r="U72" s="3">
         <v>-210700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4707,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,52 +5093,55 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>367500</v>
+      </c>
+      <c r="E76" s="3">
         <v>352900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>346900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>350100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>348500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>343000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>338700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>373400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>331200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>391800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>280800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>262100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>121600</v>
       </c>
       <c r="P76" s="3">
         <v>121600</v>
       </c>
       <c r="Q76" s="3">
-        <v>149400</v>
+        <v>121600</v>
       </c>
       <c r="R76" s="3">
         <v>149400</v>
@@ -4965,11 +5150,11 @@
         <v>149400</v>
       </c>
       <c r="T76" s="3">
+        <v>149400</v>
+      </c>
+      <c r="U76" s="3">
         <v>163600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4979,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>40633</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>12300</v>
       </c>
       <c r="E81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-62700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-22900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5256,34 +5454,37 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17400</v>
+        <v>-2500</v>
       </c>
       <c r="E89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5752,40 +5972,43 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,16 +6146,19 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-35000</v>
+        <v>24500</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -5950,46 +6179,49 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-144800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-113800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,26 +6528,29 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-4100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -6313,49 +6558,52 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>135200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>172500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>39900</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>149100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6422,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>24300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-119100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>141900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3">
         <v>-7500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>143200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>GATO</t>
   </si>
@@ -656,112 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>40633</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -831,8 +835,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -896,14 +903,17 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3">
         <v>1200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -967,14 +977,17 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,13 +1013,14 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -1014,11 +1028,11 @@
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>4</v>
@@ -1026,53 +1040,56 @@
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,49 +1159,52 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>80300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1254,38 +1277,41 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>1200</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
       <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
         <v>400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1700</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,79 +1334,83 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>84300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-4200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1388,70 +1418,73 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-16400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-84300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,70 +1520,73 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F20" s="3">
         <v>11100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-23800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,70 +1594,73 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F21" s="3">
         <v>3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-62500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>1200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-16000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-21000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-17700</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1628,19 +1668,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1649,28 +1689,28 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
@@ -1684,114 +1724,120 @@
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E23" s="3">
         <v>12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-62700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-30000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-22900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1805,8 +1851,8 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>4</v>
@@ -1814,8 +1860,8 @@
       <c r="S24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>12300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-62700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-22900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>12300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-62700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,37 +2174,40 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2158,25 +2219,25 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1600</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3">
         <v>-1800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-6900</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2338,141 +2408,147 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-11100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>23800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>12300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-62700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>12300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-62700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>40633</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,55 +2829,56 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E41" s="3">
         <v>55500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>2000</v>
       </c>
       <c r="Q41" s="3">
         <v>2000</v>
       </c>
       <c r="R41" s="3">
-        <v>9100</v>
+        <v>2000</v>
       </c>
       <c r="S41" s="3">
         <v>9100</v>
@@ -2800,11 +2887,11 @@
         <v>9100</v>
       </c>
       <c r="U41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="V41" s="3">
         <v>15600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2885,55 +2975,58 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E43" s="3">
         <v>21300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>16100</v>
       </c>
       <c r="F43" s="3">
         <v>16100</v>
       </c>
       <c r="G43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H43" s="3">
         <v>14600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>10000</v>
       </c>
       <c r="Q43" s="3">
         <v>10000</v>
       </c>
       <c r="R43" s="3">
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="S43" s="3">
         <v>6600</v>
@@ -2942,11 +3035,11 @@
         <v>6600</v>
       </c>
       <c r="U43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2998,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>100</v>
@@ -3015,8 +3111,8 @@
       <c r="U44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>4</v>
+      <c r="V44" s="3">
+        <v>100</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>4</v>
@@ -3027,55 +3123,58 @@
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>3400</v>
       </c>
       <c r="Q45" s="3">
         <v>3400</v>
       </c>
       <c r="R45" s="3">
-        <v>2600</v>
+        <v>3400</v>
       </c>
       <c r="S45" s="3">
         <v>2600</v>
@@ -3084,11 +3183,11 @@
         <v>2600</v>
       </c>
       <c r="U45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V45" s="3">
         <v>5900</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3098,55 +3197,58 @@
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E46" s="3">
         <v>78700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39600</v>
-      </c>
-      <c r="P46" s="3">
-        <v>15500</v>
       </c>
       <c r="Q46" s="3">
         <v>15500</v>
       </c>
       <c r="R46" s="3">
-        <v>18500</v>
+        <v>15500</v>
       </c>
       <c r="S46" s="3">
         <v>18500</v>
@@ -3155,11 +3257,11 @@
         <v>18500</v>
       </c>
       <c r="U46" s="3">
+        <v>18500</v>
+      </c>
+      <c r="V46" s="3">
         <v>21800</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3169,55 +3271,58 @@
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>308200</v>
+      </c>
+      <c r="E47" s="3">
         <v>321900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>328700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>354300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>352800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>347800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>341100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>342600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>379800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>333400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>393600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>247300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>226100</v>
-      </c>
-      <c r="P47" s="3">
-        <v>91500</v>
       </c>
       <c r="Q47" s="3">
         <v>91500</v>
       </c>
       <c r="R47" s="3">
-        <v>105400</v>
+        <v>91500</v>
       </c>
       <c r="S47" s="3">
         <v>105400</v>
@@ -3226,11 +3331,11 @@
         <v>105400</v>
       </c>
       <c r="U47" s="3">
+        <v>105400</v>
+      </c>
+      <c r="V47" s="3">
         <v>114400</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3240,31 +3345,34 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3272,8 +3380,8 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
+      <c r="M48" s="3">
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
@@ -3281,14 +3389,14 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>29000</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>29000</v>
       </c>
       <c r="R48" s="3">
-        <v>30200</v>
+        <v>29000</v>
       </c>
       <c r="S48" s="3">
         <v>30200</v>
@@ -3297,11 +3405,11 @@
         <v>30200</v>
       </c>
       <c r="U48" s="3">
+        <v>30200</v>
+      </c>
+      <c r="V48" s="3">
         <v>30800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3641,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3533,19 +3653,19 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -3563,10 +3683,10 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>300</v>
       </c>
       <c r="Q52" s="3">
         <v>300</v>
@@ -3583,8 +3703,8 @@
       <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
+      <c r="V52" s="3">
+        <v>300</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,55 +3789,58 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>382400</v>
+      </c>
+      <c r="E54" s="3">
         <v>400900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>379300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>381300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>382800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>383500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>358000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>352800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>388600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>345200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>408400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>284600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>265700</v>
-      </c>
-      <c r="P54" s="3">
-        <v>136100</v>
       </c>
       <c r="Q54" s="3">
         <v>136100</v>
       </c>
       <c r="R54" s="3">
-        <v>154300</v>
+        <v>136100</v>
       </c>
       <c r="S54" s="3">
         <v>154300</v>
@@ -3723,11 +3849,11 @@
         <v>154300</v>
       </c>
       <c r="U54" s="3">
+        <v>154300</v>
+      </c>
+      <c r="V54" s="3">
         <v>167200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,55 +3921,56 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>600</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>700</v>
       </c>
       <c r="R57" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="S57" s="3">
         <v>300</v>
@@ -3850,8 +3981,8 @@
       <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
+      <c r="V57" s="3">
+        <v>300</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>4</v>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3904,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>10000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>10000</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
@@ -3933,55 +4067,58 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="3">
         <v>30600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2400</v>
       </c>
       <c r="Q59" s="3">
         <v>2400</v>
       </c>
       <c r="R59" s="3">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="S59" s="3">
         <v>3200</v>
@@ -3990,11 +4127,11 @@
         <v>3200</v>
       </c>
       <c r="U59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="V59" s="3">
         <v>1800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4004,55 +4141,58 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E60" s="3">
         <v>33400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>13000</v>
       </c>
       <c r="Q60" s="3">
         <v>13000</v>
       </c>
       <c r="R60" s="3">
-        <v>3500</v>
+        <v>13000</v>
       </c>
       <c r="S60" s="3">
         <v>3500</v>
@@ -4061,11 +4201,11 @@
         <v>3500</v>
       </c>
       <c r="U60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V60" s="3">
         <v>2100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4075,8 +4215,11 @@
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4087,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>8700</v>
@@ -4096,7 +4239,7 @@
         <v>8700</v>
       </c>
       <c r="I61" s="3">
-        <v>12700</v>
+        <v>8700</v>
       </c>
       <c r="J61" s="3">
         <v>12700</v>
@@ -4105,13 +4248,13 @@
         <v>12700</v>
       </c>
       <c r="L61" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="M61" s="3">
         <v>12600</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -4146,31 +4289,34 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4188,13 +4334,13 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>1500</v>
       </c>
       <c r="R62" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="S62" s="3">
         <v>1400</v>
@@ -4205,8 +4351,8 @@
       <c r="U62" s="3">
         <v>1400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>1400</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,55 +4585,58 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E66" s="3">
         <v>33400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3500</v>
-      </c>
-      <c r="P66" s="3">
-        <v>14500</v>
       </c>
       <c r="Q66" s="3">
         <v>14500</v>
       </c>
       <c r="R66" s="3">
-        <v>4900</v>
+        <v>14500</v>
       </c>
       <c r="S66" s="3">
         <v>4900</v>
@@ -4487,11 +4645,11 @@
         <v>4900</v>
       </c>
       <c r="U66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V66" s="3">
         <v>3600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,55 +4983,58 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-183400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-185900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-198200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-201500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-197900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-198700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-203500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-207000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-172000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-213300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-150600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-135600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-149000</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-255500</v>
       </c>
       <c r="Q72" s="3">
         <v>-255500</v>
       </c>
       <c r="R72" s="3">
-        <v>-225600</v>
+        <v>-255500</v>
       </c>
       <c r="S72" s="3">
         <v>-225600</v>
@@ -4869,11 +5043,11 @@
         <v>-225600</v>
       </c>
       <c r="U72" s="3">
+        <v>-225600</v>
+      </c>
+      <c r="V72" s="3">
         <v>-210700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,55 +5279,58 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>371800</v>
+      </c>
+      <c r="E76" s="3">
         <v>367500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>352900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>346900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>350100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>348500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>343000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>338700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>373400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>331200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>391800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>280800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>262100</v>
-      </c>
-      <c r="P76" s="3">
-        <v>121600</v>
       </c>
       <c r="Q76" s="3">
         <v>121600</v>
       </c>
       <c r="R76" s="3">
-        <v>149400</v>
+        <v>121600</v>
       </c>
       <c r="S76" s="3">
         <v>149400</v>
@@ -5153,11 +5339,11 @@
         <v>149400</v>
       </c>
       <c r="U76" s="3">
+        <v>149400</v>
+      </c>
+      <c r="V76" s="3">
         <v>163600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>40633</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>12300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-62700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5457,34 +5656,37 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5975,40 +6196,43 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,20 +6376,23 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>24500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>35000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -6182,46 +6412,49 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-144800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-113800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,8 +6774,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6540,20 +6786,20 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-9000</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-4100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -6561,49 +6807,52 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>135200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>172500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>39900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>149100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>48100</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E102" s="3">
         <v>22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-119100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>141900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>-7500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>143200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>GATO</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>40633</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -838,8 +842,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -906,14 +913,17 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="3">
         <v>1200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -980,14 +990,17 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,16 +1027,17 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
+      <c r="E12" s="3">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -1031,11 +1045,11 @@
       <c r="G12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -1043,53 +1057,56 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,19 +1179,22 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
@@ -1182,32 +1202,32 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>7900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>80300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1280,38 +1303,41 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>1200</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
       <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1700</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,82 +1361,86 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>84300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-4200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1418,73 +1448,76 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-84300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,73 +1554,76 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F20" s="3">
         <v>20500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>21800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>19900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-23800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-14800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1594,73 +1631,76 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F21" s="3">
         <v>12400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-62500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>1200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-16000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-21000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-17700</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1671,19 +1711,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1692,28 +1732,28 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3">
         <v>3900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
@@ -1727,120 +1767,126 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-62700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-22900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1854,8 +1900,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
@@ -1863,8 +1909,8 @@
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-62700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-22900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-62700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-30000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-22900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2203,14 +2264,14 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>4</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2222,25 +2283,25 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-5400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1600</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U29" s="3">
         <v>-1800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-6900</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2408,147 +2478,153 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-20500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-21800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-19900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>23800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>14800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-62700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-30000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-14900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-22900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-62700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-30000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-14900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-22900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>40633</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,58 +2916,59 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E41" s="3">
         <v>70600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>55500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>2000</v>
       </c>
       <c r="R41" s="3">
         <v>2000</v>
       </c>
       <c r="S41" s="3">
-        <v>9100</v>
+        <v>2000</v>
       </c>
       <c r="T41" s="3">
         <v>9100</v>
@@ -2890,11 +2977,11 @@
         <v>9100</v>
       </c>
       <c r="V41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="W41" s="3">
         <v>15600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2904,8 +2991,11 @@
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2978,58 +3068,61 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21300</v>
-      </c>
-      <c r="F43" s="3">
-        <v>16100</v>
       </c>
       <c r="G43" s="3">
         <v>16100</v>
       </c>
       <c r="H43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I43" s="3">
         <v>14600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>10000</v>
       </c>
       <c r="R43" s="3">
         <v>10000</v>
       </c>
       <c r="S43" s="3">
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="T43" s="3">
         <v>6600</v>
@@ -3038,11 +3131,11 @@
         <v>6600</v>
       </c>
       <c r="V43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3097,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -3114,8 +3210,8 @@
       <c r="V44" s="3">
         <v>100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
+      <c r="W44" s="3">
+        <v>100</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>4</v>
@@ -3126,58 +3222,61 @@
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>3400</v>
       </c>
       <c r="R45" s="3">
         <v>3400</v>
       </c>
       <c r="S45" s="3">
-        <v>2600</v>
+        <v>3400</v>
       </c>
       <c r="T45" s="3">
         <v>2600</v>
@@ -3186,11 +3285,11 @@
         <v>2600</v>
       </c>
       <c r="V45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="W45" s="3">
         <v>5900</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3200,58 +3299,61 @@
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E46" s="3">
         <v>73500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>78700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39600</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>15500</v>
       </c>
       <c r="R46" s="3">
         <v>15500</v>
       </c>
       <c r="S46" s="3">
-        <v>18500</v>
+        <v>15500</v>
       </c>
       <c r="T46" s="3">
         <v>18500</v>
@@ -3260,11 +3362,11 @@
         <v>18500</v>
       </c>
       <c r="V46" s="3">
+        <v>18500</v>
+      </c>
+      <c r="W46" s="3">
         <v>21800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3274,58 +3376,61 @@
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E47" s="3">
         <v>308200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>321900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>328700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>354300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>352800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>347800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>341100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>342600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>379800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>333400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>393600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>247300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>226100</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>91500</v>
       </c>
       <c r="R47" s="3">
         <v>91500</v>
       </c>
       <c r="S47" s="3">
-        <v>105400</v>
+        <v>91500</v>
       </c>
       <c r="T47" s="3">
         <v>105400</v>
@@ -3334,11 +3439,11 @@
         <v>105400</v>
       </c>
       <c r="V47" s="3">
+        <v>105400</v>
+      </c>
+      <c r="W47" s="3">
         <v>114400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3348,16 +3453,19 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
+      <c r="E48" s="3">
+        <v>400</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>4</v>
@@ -3374,8 +3482,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3383,8 +3491,8 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
@@ -3392,14 +3500,14 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>29000</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>29000</v>
       </c>
       <c r="S48" s="3">
-        <v>30200</v>
+        <v>29000</v>
       </c>
       <c r="T48" s="3">
         <v>30200</v>
@@ -3408,11 +3516,11 @@
         <v>30200</v>
       </c>
       <c r="V48" s="3">
+        <v>30200</v>
+      </c>
+      <c r="W48" s="3">
         <v>30800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,31 +3761,34 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3686,10 +3806,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>300</v>
       </c>
       <c r="R52" s="3">
         <v>300</v>
@@ -3706,8 +3826,8 @@
       <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
+      <c r="W52" s="3">
+        <v>300</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>4</v>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,58 +3915,61 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>390000</v>
+      </c>
+      <c r="E54" s="3">
         <v>382400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>400900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>381300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>382800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>383500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>358000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>352800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>388600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>345200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>408400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>284600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>265700</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>136100</v>
       </c>
       <c r="R54" s="3">
         <v>136100</v>
       </c>
       <c r="S54" s="3">
-        <v>154300</v>
+        <v>136100</v>
       </c>
       <c r="T54" s="3">
         <v>154300</v>
@@ -3852,11 +3978,11 @@
         <v>154300</v>
       </c>
       <c r="V54" s="3">
+        <v>154300</v>
+      </c>
+      <c r="W54" s="3">
         <v>167200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,58 +4052,59 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>500</v>
       </c>
       <c r="I57" s="3">
+        <v>500</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R57" s="3">
         <v>700</v>
       </c>
       <c r="S57" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="T57" s="3">
         <v>300</v>
@@ -3984,8 +4115,8 @@
       <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
+      <c r="W57" s="3">
+        <v>300</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>4</v>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4041,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>10000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="S58" s="3">
+        <v>10000</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -4070,58 +4204,61 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E59" s="3">
         <v>10000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2400</v>
       </c>
       <c r="R59" s="3">
         <v>2400</v>
       </c>
       <c r="S59" s="3">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="T59" s="3">
         <v>3200</v>
@@ -4130,11 +4267,11 @@
         <v>3200</v>
       </c>
       <c r="V59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W59" s="3">
         <v>1800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4144,58 +4281,61 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E60" s="3">
         <v>10400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>13000</v>
       </c>
       <c r="R60" s="3">
         <v>13000</v>
       </c>
       <c r="S60" s="3">
-        <v>3500</v>
+        <v>13000</v>
       </c>
       <c r="T60" s="3">
         <v>3500</v>
@@ -4204,11 +4344,11 @@
         <v>3500</v>
       </c>
       <c r="V60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="W60" s="3">
         <v>2100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4218,8 +4358,11 @@
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4233,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>8700</v>
@@ -4242,7 +4385,7 @@
         <v>8700</v>
       </c>
       <c r="J61" s="3">
-        <v>12700</v>
+        <v>8700</v>
       </c>
       <c r="K61" s="3">
         <v>12700</v>
@@ -4251,13 +4394,13 @@
         <v>12700</v>
       </c>
       <c r="M61" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="N61" s="3">
         <v>12600</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -4292,17 +4435,20 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4318,8 +4464,8 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4337,13 +4483,13 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>1500</v>
       </c>
       <c r="S62" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="T62" s="3">
         <v>1400</v>
@@ -4354,8 +4500,8 @@
       <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
+      <c r="W62" s="3">
+        <v>1400</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>4</v>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,58 +4743,61 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E66" s="3">
         <v>10600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>14500</v>
       </c>
       <c r="R66" s="3">
         <v>14500</v>
       </c>
       <c r="S66" s="3">
-        <v>4900</v>
+        <v>14500</v>
       </c>
       <c r="T66" s="3">
         <v>4900</v>
@@ -4648,11 +4806,11 @@
         <v>4900</v>
       </c>
       <c r="V66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="W66" s="3">
         <v>3600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,58 +5157,61 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-174200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-183400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-185900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-198200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-201500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-197900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-198700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-203500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-207000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-172000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-213300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-150600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-135600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-149000</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-255500</v>
       </c>
       <c r="R72" s="3">
         <v>-255500</v>
       </c>
       <c r="S72" s="3">
-        <v>-225600</v>
+        <v>-255500</v>
       </c>
       <c r="T72" s="3">
         <v>-225600</v>
@@ -5046,11 +5220,11 @@
         <v>-225600</v>
       </c>
       <c r="V72" s="3">
+        <v>-225600</v>
+      </c>
+      <c r="W72" s="3">
         <v>-210700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,58 +5465,61 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>380900</v>
+      </c>
+      <c r="E76" s="3">
         <v>371800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>367500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>352900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>346900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>350100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>348500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>343000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>338700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>373400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>331200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>391800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>280800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>262100</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>121600</v>
       </c>
       <c r="R76" s="3">
         <v>121600</v>
       </c>
       <c r="S76" s="3">
-        <v>149400</v>
+        <v>121600</v>
       </c>
       <c r="T76" s="3">
         <v>149400</v>
@@ -5342,11 +5528,11 @@
         <v>149400</v>
       </c>
       <c r="V76" s="3">
+        <v>149400</v>
+      </c>
+      <c r="W76" s="3">
         <v>163600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>40633</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-62700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-30000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-14900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-22900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5659,34 +5858,37 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>15100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,8 +6377,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6199,40 +6420,43 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,23 +6606,26 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>24500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -6415,46 +6645,49 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-144800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-113800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,32 +7020,35 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-9000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-4100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -6810,49 +7056,52 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>135200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>172500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>39900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>149100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>48100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E102" s="3">
         <v>15100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-119100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>141900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3">
         <v>-7500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>143200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GATO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>GATO</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>40633</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -845,8 +849,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -916,14 +923,17 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="3">
         <v>1200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -993,14 +1003,17 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,16 +1041,17 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -1048,8 +1062,8 @@
       <c r="H12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -1060,53 +1074,56 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,22 +1199,25 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>5300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
@@ -1205,32 +1225,32 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>7900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>80300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1306,38 +1329,41 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
         <v>1200</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
       <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7000</v>
       </c>
-      <c r="F17" s="3">
-        <v>8000</v>
-      </c>
       <c r="G17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H17" s="3">
         <v>7500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>84300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-4200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-5300</v>
       </c>
       <c r="E18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-8000</v>
-      </c>
       <c r="G18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-84300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-18500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,188 +1578,195 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-19700</v>
       </c>
       <c r="E20" s="3">
-        <v>9600</v>
+        <v>-16100</v>
       </c>
       <c r="F20" s="3">
-        <v>20500</v>
+        <v>-8800</v>
       </c>
       <c r="G20" s="3">
-        <v>11100</v>
+        <v>-19100</v>
       </c>
       <c r="H20" s="3">
-        <v>2800</v>
+        <v>-10700</v>
       </c>
       <c r="I20" s="3">
-        <v>6600</v>
+        <v>-2600</v>
       </c>
       <c r="J20" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="K20" s="3">
         <v>14700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>21800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-15000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>14400</v>
       </c>
       <c r="E21" s="3">
-        <v>2600</v>
+        <v>8200</v>
       </c>
       <c r="F21" s="3">
-        <v>12400</v>
+        <v>1800</v>
       </c>
       <c r="G21" s="3">
-        <v>3600</v>
+        <v>16000</v>
       </c>
       <c r="H21" s="3">
-        <v>-3400</v>
+        <v>3200</v>
       </c>
       <c r="I21" s="3">
-        <v>1000</v>
+        <v>-3500</v>
       </c>
       <c r="J21" s="3">
+        <v>900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-62500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1600</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-16000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-21000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-17700</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1735,28 +1775,28 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3">
         <v>3900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
@@ -1770,126 +1810,132 @@
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E23" s="3">
         <v>9300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-62700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-22900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-20100</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1903,8 +1949,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
@@ -1912,8 +1958,8 @@
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-62700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-22900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-62700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-22900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2267,14 +2328,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>4</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2286,25 +2347,25 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-5400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1600</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-6900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,162 +2536,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>19700</v>
       </c>
       <c r="E32" s="3">
-        <v>-9600</v>
+        <v>16100</v>
       </c>
       <c r="F32" s="3">
-        <v>-20500</v>
+        <v>8800</v>
       </c>
       <c r="G32" s="3">
-        <v>-11100</v>
+        <v>19100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2800</v>
+        <v>10700</v>
       </c>
       <c r="I32" s="3">
-        <v>-6600</v>
+        <v>2600</v>
       </c>
       <c r="J32" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-21800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>15000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-62700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-22900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-62700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-22900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>40633</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,61 +3003,62 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E41" s="3">
         <v>82500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>70600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>55500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>2000</v>
       </c>
       <c r="S41" s="3">
         <v>2000</v>
       </c>
       <c r="T41" s="3">
-        <v>9100</v>
+        <v>2000</v>
       </c>
       <c r="U41" s="3">
         <v>9100</v>
@@ -2980,11 +3067,11 @@
         <v>9100</v>
       </c>
       <c r="W41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="X41" s="3">
         <v>15600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2994,8 +3081,11 @@
       <c r="AA41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,61 +3161,64 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
-        <v>1600</v>
-      </c>
       <c r="F43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G43" s="3">
         <v>21300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>16100</v>
       </c>
       <c r="H43" s="3">
         <v>16100</v>
       </c>
       <c r="I43" s="3">
-        <v>14600</v>
+        <v>3000</v>
       </c>
       <c r="J43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K43" s="3">
         <v>15600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5200</v>
-      </c>
-      <c r="R43" s="3">
-        <v>10000</v>
       </c>
       <c r="S43" s="3">
         <v>10000</v>
       </c>
       <c r="T43" s="3">
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="U43" s="3">
         <v>6600</v>
@@ -3134,11 +3227,11 @@
         <v>6600</v>
       </c>
       <c r="W43" s="3">
+        <v>6600</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3148,31 +3241,34 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3196,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>100</v>
@@ -3213,8 +3309,8 @@
       <c r="W44" s="3">
         <v>100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>4</v>
+      <c r="X44" s="3">
+        <v>100</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>4</v>
@@ -3225,61 +3321,64 @@
       <c r="AA44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>3400</v>
       </c>
       <c r="S45" s="3">
         <v>3400</v>
       </c>
       <c r="T45" s="3">
-        <v>2600</v>
+        <v>3400</v>
       </c>
       <c r="U45" s="3">
         <v>2600</v>
@@ -3288,11 +3387,11 @@
         <v>2600</v>
       </c>
       <c r="W45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X45" s="3">
         <v>5900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3302,61 +3401,64 @@
       <c r="AA45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E46" s="3">
         <v>84200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>78700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39600</v>
-      </c>
-      <c r="R46" s="3">
-        <v>15500</v>
       </c>
       <c r="S46" s="3">
         <v>15500</v>
       </c>
       <c r="T46" s="3">
-        <v>18500</v>
+        <v>15500</v>
       </c>
       <c r="U46" s="3">
         <v>18500</v>
@@ -3365,11 +3467,11 @@
         <v>18500</v>
       </c>
       <c r="W46" s="3">
+        <v>18500</v>
+      </c>
+      <c r="X46" s="3">
         <v>21800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3379,61 +3481,64 @@
       <c r="AA46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>285500</v>
+      </c>
+      <c r="E47" s="3">
         <v>305200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>308200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>321900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>328700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>354300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>352800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>347800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>341100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>342600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>379800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>333400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>393600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>247300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>226100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>91500</v>
       </c>
       <c r="S47" s="3">
         <v>91500</v>
       </c>
       <c r="T47" s="3">
-        <v>105400</v>
+        <v>91500</v>
       </c>
       <c r="U47" s="3">
         <v>105400</v>
@@ -3442,11 +3547,11 @@
         <v>105400</v>
       </c>
       <c r="W47" s="3">
+        <v>105400</v>
+      </c>
+      <c r="X47" s="3">
         <v>114400</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3456,13 +3561,16 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
         <v>400</v>
@@ -3485,8 +3593,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3494,8 +3602,8 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -3503,14 +3611,14 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R48" s="3">
-        <v>29000</v>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>29000</v>
       </c>
       <c r="T48" s="3">
-        <v>30200</v>
+        <v>29000</v>
       </c>
       <c r="U48" s="3">
         <v>30200</v>
@@ -3519,11 +3627,11 @@
         <v>30200</v>
       </c>
       <c r="W48" s="3">
+        <v>30200</v>
+      </c>
+      <c r="X48" s="3">
         <v>30800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,19 +3881,22 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -3785,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3809,10 +3929,10 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>300</v>
       </c>
       <c r="S52" s="3">
         <v>300</v>
@@ -3829,8 +3949,8 @@
       <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
+      <c r="X52" s="3">
+        <v>300</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>4</v>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,61 +4041,64 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E54" s="3">
         <v>390000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>382400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>400900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>381300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>382800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>383500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>358000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>352800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>388600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>345200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>408400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>284600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>265700</v>
-      </c>
-      <c r="R54" s="3">
-        <v>136100</v>
       </c>
       <c r="S54" s="3">
         <v>136100</v>
       </c>
       <c r="T54" s="3">
-        <v>154300</v>
+        <v>136100</v>
       </c>
       <c r="U54" s="3">
         <v>154300</v>
@@ -3981,11 +4107,11 @@
         <v>154300</v>
       </c>
       <c r="W54" s="3">
+        <v>154300</v>
+      </c>
+      <c r="X54" s="3">
         <v>167200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,61 +4183,62 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
       </c>
       <c r="I57" s="3">
         <v>500</v>
       </c>
       <c r="J57" s="3">
+        <v>500</v>
+      </c>
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
       <c r="R57" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S57" s="3">
         <v>700</v>
       </c>
       <c r="T57" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
@@ -4118,8 +4249,8 @@
       <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
+      <c r="X57" s="3">
+        <v>300</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>4</v>
@@ -4130,8 +4261,11 @@
       <c r="AA57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4151,10 +4285,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4178,13 +4312,13 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>10000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
+      <c r="T58" s="3">
+        <v>10000</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
@@ -4207,61 +4341,64 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8700</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
-        <v>30600</v>
+        <v>3500</v>
       </c>
       <c r="G59" s="3">
-        <v>25300</v>
+        <v>24400</v>
       </c>
       <c r="H59" s="3">
-        <v>25200</v>
+        <v>21000</v>
       </c>
       <c r="I59" s="3">
-        <v>23600</v>
+        <v>21000</v>
       </c>
       <c r="J59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K59" s="3">
         <v>25800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>2400</v>
       </c>
       <c r="S59" s="3">
         <v>2400</v>
       </c>
       <c r="T59" s="3">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="U59" s="3">
         <v>3200</v>
@@ -4270,11 +4407,11 @@
         <v>3200</v>
       </c>
       <c r="W59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4284,61 +4421,64 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E60" s="3">
         <v>8900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>13000</v>
       </c>
       <c r="S60" s="3">
         <v>13000</v>
       </c>
       <c r="T60" s="3">
-        <v>3500</v>
+        <v>13000</v>
       </c>
       <c r="U60" s="3">
         <v>3500</v>
@@ -4347,11 +4487,11 @@
         <v>3500</v>
       </c>
       <c r="W60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="X60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4361,25 +4501,28 @@
       <c r="AA60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>8700</v>
@@ -4388,7 +4531,7 @@
         <v>8700</v>
       </c>
       <c r="K61" s="3">
-        <v>12700</v>
+        <v>8700</v>
       </c>
       <c r="L61" s="3">
         <v>12700</v>
@@ -4397,13 +4540,13 @@
         <v>12700</v>
       </c>
       <c r="N61" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="O61" s="3">
         <v>12600</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4438,16 +4581,19 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>300</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
@@ -4467,8 +4613,8 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4486,13 +4632,13 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>1500</v>
       </c>
       <c r="T62" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="U62" s="3">
         <v>1400</v>
@@ -4503,8 +4649,8 @@
       <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="X62" s="3">
+        <v>1400</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,61 +4901,64 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E66" s="3">
         <v>9200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3500</v>
-      </c>
-      <c r="R66" s="3">
-        <v>14500</v>
       </c>
       <c r="S66" s="3">
         <v>14500</v>
       </c>
       <c r="T66" s="3">
-        <v>4900</v>
+        <v>14500</v>
       </c>
       <c r="U66" s="3">
         <v>4900</v>
@@ -4809,11 +4967,11 @@
         <v>4900</v>
       </c>
       <c r="W66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="X66" s="3">
         <v>3600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,61 +5331,64 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-174200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-183400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-185900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-198200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-201500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-197900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-198700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-203500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-207000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-172000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-213300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-150600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-135600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-149000</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-255500</v>
       </c>
       <c r="S72" s="3">
         <v>-255500</v>
       </c>
       <c r="T72" s="3">
-        <v>-225600</v>
+        <v>-255500</v>
       </c>
       <c r="U72" s="3">
         <v>-225600</v>
@@ -5223,11 +5397,11 @@
         <v>-225600</v>
       </c>
       <c r="W72" s="3">
+        <v>-225600</v>
+      </c>
+      <c r="X72" s="3">
         <v>-210700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,61 +5651,64 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E76" s="3">
         <v>380900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>371800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>367500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>352900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>346900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>350100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>348500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>343000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>338700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>373400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>331200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>391800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>280800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>262100</v>
-      </c>
-      <c r="R76" s="3">
-        <v>121600</v>
       </c>
       <c r="S76" s="3">
         <v>121600</v>
       </c>
       <c r="T76" s="3">
-        <v>149400</v>
+        <v>121600</v>
       </c>
       <c r="U76" s="3">
         <v>149400</v>
@@ -5531,11 +5717,11 @@
         <v>149400</v>
       </c>
       <c r="W76" s="3">
+        <v>149400</v>
+      </c>
+      <c r="X76" s="3">
         <v>163600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>40633</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>40543</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-62700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-22900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6008,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5861,34 +6060,37 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E89" s="3">
         <v>11800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15100</v>
       </c>
-      <c r="F89" s="3">
-        <v>-2500</v>
-      </c>
       <c r="G89" s="3">
-        <v>-1700</v>
+        <v>57000</v>
       </c>
       <c r="H89" s="3">
+        <v>33300</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,31 +6598,32 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6423,40 +6644,43 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,8 +6836,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6620,20 +6850,20 @@
       <c r="E94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="3">
-        <v>24500</v>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
-        <v>35000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-35000</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6648,46 +6878,49 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-144800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-113800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,31 +6948,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,35 +7266,38 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-9000</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -7059,72 +7305,75 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>135200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>172500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>39900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>149100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>48100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E102" s="3">
         <v>11900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-119100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>141900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>-7500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>143200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1300</v>
       </c>
     </row>
